--- a/CODFEST_Registered_Teams_and_Members.xlsx
+++ b/CODFEST_Registered_Teams_and_Members.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P12"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -474,19 +474,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>DRAGONFIRE</v>
+        <v>Rosa Kekulu A</v>
       </c>
       <c r="C2" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D2" t="str">
-        <v>Kasun Lakshan</v>
+        <v>Navida Sandiv Gamage</v>
       </c>
       <c r="E2" t="str">
-        <v>unikasun55@gmail.com</v>
+        <v>navidasandiv@gmail.com</v>
       </c>
       <c r="F2" t="str">
-        <v>+94704180640</v>
+        <v>+94718833133</v>
       </c>
       <c r="G2" t="str">
         <v>—</v>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="str">
-        <v>14/8/2026, 10:23:21 pm</v>
+        <v>14/8/2026, 11:12:46 pm</v>
       </c>
     </row>
     <row r="3">
@@ -524,19 +524,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Ghost Unit</v>
+        <v>Rosa Kekulu B</v>
       </c>
       <c r="C3" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D3" t="str">
-        <v>Thilina Ravishan</v>
+        <v>Savindu mihiran</v>
       </c>
       <c r="E3" t="str">
-        <v>thilinaravishan2003@gmail.com</v>
+        <v>savindumihiran12345@gmail.com</v>
       </c>
       <c r="F3" t="str">
-        <v>+94767852670</v>
+        <v>+94762934155</v>
       </c>
       <c r="G3" t="str">
         <v>—</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="str">
-        <v>14/8/2026, 10:16:56 pm</v>
+        <v>14/8/2026, 11:10:49 pm</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +574,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>ShadowX</v>
+        <v>The Annabelles</v>
       </c>
       <c r="C4" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D4" t="str">
-        <v xml:space="preserve">Thathsarani Thenujana </v>
+        <v>leader</v>
       </c>
       <c r="E4" t="str">
-        <v>thathsaranithenujana@gmail.com</v>
+        <v>induminipabasara1@gmail.com</v>
       </c>
       <c r="F4" t="str">
-        <v>+94785600006</v>
+        <v>+94704897405</v>
       </c>
       <c r="G4" t="str">
         <v>—</v>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="str">
-        <v>14/8/2026, 9:27:36 pm</v>
+        <v>14/8/2026, 11:02:15 pm</v>
       </c>
     </row>
     <row r="5">
@@ -624,19 +624,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Hithuwakkarayo</v>
+        <v>DRAGONFIRE</v>
       </c>
       <c r="C5" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D5" t="str">
-        <v xml:space="preserve">Harsha madhubashana </v>
+        <v>Kasun Lakshan</v>
       </c>
       <c r="E5" t="str">
-        <v>subash11246@gmail.com</v>
+        <v>unikasun55@gmail.com</v>
       </c>
       <c r="F5" t="str">
-        <v>+94721508452</v>
+        <v>+94704180640</v>
       </c>
       <c r="G5" t="str">
         <v>—</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="str">
-        <v>14/8/2026, 9:12:06 pm</v>
+        <v>14/8/2026, 10:23:21 pm</v>
       </c>
     </row>
     <row r="6">
@@ -674,19 +674,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Team Vnix</v>
+        <v>Ghost Unit</v>
       </c>
       <c r="C6" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D6" t="str">
-        <v>Naveen Hiranya</v>
+        <v>Thilina Ravishan</v>
       </c>
       <c r="E6" t="str">
-        <v>naveenhiranya999@gmail.com</v>
+        <v>thilinaravishan2003@gmail.com</v>
       </c>
       <c r="F6" t="str">
-        <v>+94756067029</v>
+        <v>+94767852670</v>
       </c>
       <c r="G6" t="str">
         <v>—</v>
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="str">
-        <v>14/8/2026, 8:20:03 pm</v>
+        <v>14/8/2026, 10:16:56 pm</v>
       </c>
     </row>
     <row r="7">
@@ -724,19 +724,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Little Princess</v>
+        <v>ShadowX</v>
       </c>
       <c r="C7" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D7" t="str">
-        <v>Randesh Daluwatte</v>
+        <v xml:space="preserve">Thathsarani Thenujana </v>
       </c>
       <c r="E7" t="str">
-        <v>randesh123@gmail.com</v>
+        <v>thathsaranithenujana@gmail.com</v>
       </c>
       <c r="F7" t="str">
-        <v>+94775671929</v>
+        <v>+94785600006</v>
       </c>
       <c r="G7" t="str">
         <v>—</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="str">
-        <v>14/8/2026, 7:31:10 pm</v>
+        <v>14/8/2026, 9:27:36 pm</v>
       </c>
     </row>
     <row r="8">
@@ -774,19 +774,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Phantom Squad</v>
+        <v>Hithuwakkarayo</v>
       </c>
       <c r="C8" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D8" t="str">
-        <v>Sudhari Rajakaruna</v>
+        <v xml:space="preserve">Harsha madhubashana </v>
       </c>
       <c r="E8" t="str">
-        <v>sudharirajakaruna2005@gmail.com</v>
+        <v>subash11246@gmail.com</v>
       </c>
       <c r="F8" t="str">
-        <v>+94777531210</v>
+        <v>+94721508452</v>
       </c>
       <c r="G8" t="str">
         <v>—</v>
@@ -798,10 +798,10 @@
         <v>4</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -810,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="str">
-        <v>14/8/2026, 6:28:53 pm</v>
+        <v>14/8/2026, 9:12:06 pm</v>
       </c>
     </row>
     <row r="9">
@@ -824,19 +824,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>VEX</v>
+        <v>Team Vnix</v>
       </c>
       <c r="C9" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D9" t="str">
-        <v>JEZAN N</v>
+        <v>Naveen Hiranya</v>
       </c>
       <c r="E9" t="str">
-        <v>jezanjoy@gmail.com</v>
+        <v>naveenhiranya999@gmail.com</v>
       </c>
       <c r="F9" t="str">
-        <v>+94754860486</v>
+        <v>+94756067029</v>
       </c>
       <c r="G9" t="str">
         <v>—</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="str">
-        <v>14/8/2026, 5:00:20 pm</v>
+        <v>14/8/2026, 8:20:03 pm</v>
       </c>
     </row>
     <row r="10">
@@ -874,19 +874,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>The Annabelles</v>
+        <v>Little Princess</v>
       </c>
       <c r="C10" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D10" t="str">
-        <v>Kumanayakage pabasara indumini</v>
+        <v>Randesh Daluwatte</v>
       </c>
       <c r="E10" t="str">
-        <v>induminipabasara1@gmail.com</v>
+        <v>randesh123@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>+94704897405</v>
+        <v>+94775671929</v>
       </c>
       <c r="G10" t="str">
         <v>—</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -913,22 +913,122 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="str">
-        <v>14/8/2026, 12:50:52 pm</v>
+        <v>14/8/2026, 7:31:10 pm</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Phantom Squad</v>
+      </c>
+      <c r="C11" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Sudhari Rajakaruna</v>
+      </c>
+      <c r="E11" t="str">
+        <v>sudharirajakaruna2005@gmail.com</v>
+      </c>
+      <c r="F11" t="str">
+        <v>+94777531210</v>
+      </c>
+      <c r="G11" t="str">
+        <v>—</v>
+      </c>
+      <c r="H11" t="str">
+        <v>—</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="str">
+        <v>14/8/2026, 6:28:53 pm</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>VEX</v>
+      </c>
+      <c r="C12" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D12" t="str">
+        <v>JEZAN N</v>
+      </c>
+      <c r="E12" t="str">
+        <v>jezanjoy@gmail.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>+94754860486</v>
+      </c>
+      <c r="G12" t="str">
+        <v>—</v>
+      </c>
+      <c r="H12" t="str">
+        <v>—</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="str">
+        <v>14/8/2026, 5:00:20 pm</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I45"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -975,22 +1075,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>DRAGONFIRE</v>
+        <v>Rosa Kekulu A</v>
       </c>
       <c r="C2" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D2" t="str">
-        <v>Kanishka Kisal</v>
+        <v>Sithum Adhikaranayake</v>
       </c>
       <c r="E2" t="str">
-        <v>Caraxes</v>
+        <v>KIVIER</v>
       </c>
       <c r="F2" t="str">
-        <v>kanishkakisaldhanawardana@gmail.com</v>
+        <v>itsnotsithum@gmail.com</v>
       </c>
       <c r="G2" t="str">
-        <v>+94710938105</v>
+        <v>+94714018738</v>
       </c>
       <c r="H2" t="str">
         <v>—</v>
@@ -1004,22 +1104,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>DRAGONFIRE</v>
+        <v>Rosa Kekulu A</v>
       </c>
       <c r="C3" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D3" t="str">
-        <v>Mihindu Udayakanha</v>
+        <v>Pasindu Ruwanpathirana</v>
       </c>
       <c r="E3" t="str">
-        <v>Vhagar</v>
+        <v>Scalesteep</v>
       </c>
       <c r="F3" t="str">
-        <v>mihinduuayakanha0404@gmail.com</v>
+        <v>bimsarapasindurp@gmail.com</v>
       </c>
       <c r="G3" t="str">
-        <v>+94714088850</v>
+        <v>+94715726416</v>
       </c>
       <c r="H3" t="str">
         <v>—</v>
@@ -1033,22 +1133,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>DRAGONFIRE</v>
+        <v>Rosa Kekulu A</v>
       </c>
       <c r="C4" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D4" t="str">
-        <v>Shaminda hettiarachchi</v>
+        <v>Luchitha Navaratne</v>
       </c>
       <c r="E4" t="str">
-        <v>Cannibal</v>
+        <v>luvia</v>
       </c>
       <c r="F4" t="str">
-        <v>shamindashaminda66@gmail.com</v>
+        <v>lonathluchitha@gmail.com</v>
       </c>
       <c r="G4" t="str">
-        <v>+94077398991</v>
+        <v>+94706680588</v>
       </c>
       <c r="H4" t="str">
         <v>—</v>
@@ -1062,22 +1162,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>DRAGONFIRE</v>
+        <v>Rosa Kekulu A</v>
       </c>
       <c r="C5" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D5" t="str">
-        <v>Suneth Gevindu</v>
+        <v>Shehan Nimsara</v>
       </c>
       <c r="E5" t="str">
-        <v>NIGHTFURY</v>
+        <v>Aizen</v>
       </c>
       <c r="F5" t="str">
-        <v>gevindusuneth@gmail.com</v>
+        <v>shehannimsara@gmail.com</v>
       </c>
       <c r="G5" t="str">
-        <v>+94771520870</v>
+        <v>+94783890996</v>
       </c>
       <c r="H5" t="str">
         <v>—</v>
@@ -1091,22 +1191,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Ghost Unit</v>
+        <v>Rosa Kekulu B</v>
       </c>
       <c r="C6" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D6" t="str">
-        <v>Janith Imalsha</v>
+        <v>A.S.Tharu Gimhana silva</v>
       </c>
       <c r="E6" t="str">
-        <v>Dark_Knight</v>
+        <v>StarLord</v>
       </c>
       <c r="F6" t="str">
-        <v>janithimalsha34@gmail.com</v>
+        <v>shehantharu2095@gmail.com</v>
       </c>
       <c r="G6" t="str">
-        <v>+94712248323</v>
+        <v>+94712302182</v>
       </c>
       <c r="H6" t="str">
         <v>—</v>
@@ -1120,22 +1220,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Ghost Unit</v>
+        <v>Rosa Kekulu B</v>
       </c>
       <c r="C7" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D7" t="str">
-        <v>Adithya Prabhashwara</v>
+        <v>L.P Kaveen Roshana Liyanapathirana</v>
       </c>
       <c r="E7" t="str">
-        <v>Dark_Fury</v>
+        <v>Zyren</v>
       </c>
       <c r="F7" t="str">
-        <v>adithyaprabhashwaraADI@gmail.com</v>
+        <v>kaveen.roshana@gmail.com</v>
       </c>
       <c r="G7" t="str">
-        <v>+94713582875</v>
+        <v>+94762862215</v>
       </c>
       <c r="H7" t="str">
         <v>—</v>
@@ -1149,22 +1249,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Ghost Unit</v>
+        <v>Rosa Kekulu B</v>
       </c>
       <c r="C8" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D8" t="str">
-        <v>Thilina Prabhath</v>
+        <v>Thinuga Sesanda</v>
       </c>
       <c r="E8" t="str">
-        <v>Dark_Moon</v>
+        <v>TeraX</v>
       </c>
       <c r="F8" t="str">
-        <v>prabhathsriguruge@gmail.com</v>
+        <v>thinugasesanda2005@gmail.com</v>
       </c>
       <c r="G8" t="str">
-        <v>+94778487612</v>
+        <v>+94712052080</v>
       </c>
       <c r="H8" t="str">
         <v>—</v>
@@ -1178,22 +1278,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Ghost Unit</v>
+        <v>Rosa Kekulu B</v>
       </c>
       <c r="C9" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D9" t="str">
-        <v>Dineth Thilanka</v>
+        <v>S.L.K. Prabhashana</v>
       </c>
       <c r="E9" t="str">
-        <v>Dark_Soul</v>
+        <v>Kingslayer</v>
       </c>
       <c r="F9" t="str">
-        <v>dineththilanka2500@gmail.com</v>
+        <v>slkprabhashana@gmail.com</v>
       </c>
       <c r="G9" t="str">
-        <v>+94705252514</v>
+        <v>+94719567174</v>
       </c>
       <c r="H9" t="str">
         <v>—</v>
@@ -1207,22 +1307,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>ShadowX</v>
+        <v>The Annabelles</v>
       </c>
       <c r="C10" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D10" t="str">
-        <v>Ranasinghe Jayathri Nameetha</v>
+        <v>R.P.S.A.Keshani</v>
       </c>
       <c r="E10" t="str">
-        <v>One Tap</v>
+        <v>Zeraphy</v>
       </c>
       <c r="F10" t="str">
-        <v>Ranasranasinghejayathri7@gmail.com</v>
+        <v>sanduniamasha876@gmail.com</v>
       </c>
       <c r="G10" t="str">
-        <v>+94071152716</v>
+        <v>+94760667655</v>
       </c>
       <c r="H10" t="str">
         <v>—</v>
@@ -1236,22 +1336,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>ShadowX</v>
+        <v>The Annabelles</v>
       </c>
       <c r="C11" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D11" t="str">
-        <v>R.M.Tharani Chathurya Rathnayaka</v>
+        <v>Dewage Sandima Umayanjalee De Silva</v>
       </c>
       <c r="E11" t="str">
-        <v>Deeva</v>
+        <v>RoxyFire</v>
       </c>
       <c r="F11" t="str">
-        <v>tharanichathurya9@gmail.com</v>
+        <v>sandimaumayanjalee2005@gmail.com</v>
       </c>
       <c r="G11" t="str">
-        <v>+94761285825</v>
+        <v>+94721469871</v>
       </c>
       <c r="H11" t="str">
         <v>—</v>
@@ -1265,22 +1365,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>ShadowX</v>
+        <v>The Annabelles</v>
       </c>
       <c r="C12" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D12" t="str">
-        <v xml:space="preserve">Shashmila Laknadi </v>
+        <v>D M V I Dissanayake</v>
       </c>
       <c r="E12" t="str">
-        <v>Zia</v>
+        <v>Vortex</v>
       </c>
       <c r="F12" t="str">
-        <v>shashmilalaknadi24@gmail.com</v>
+        <v>vishmi.dissanayake1122@gmail.com</v>
       </c>
       <c r="G12" t="str">
-        <v>+94784201134</v>
+        <v>+94788943505</v>
       </c>
       <c r="H12" t="str">
         <v>—</v>
@@ -1294,22 +1394,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>ShadowX</v>
+        <v>The Annabelles</v>
       </c>
       <c r="C13" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D13" t="str">
-        <v>Subenthiran Kajani</v>
+        <v>Yashmi Amadhi Rajapakse</v>
       </c>
       <c r="E13" t="str">
-        <v>Zena</v>
+        <v>Andromeda</v>
       </c>
       <c r="F13" t="str">
-        <v>subenthirankajani35@gmail.com</v>
+        <v>yashamax555@gmail.com</v>
       </c>
       <c r="G13" t="str">
-        <v>+94719170183</v>
+        <v>+94778568529</v>
       </c>
       <c r="H13" t="str">
         <v>—</v>
@@ -1323,22 +1423,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Hithuwakkarayo</v>
+        <v>DRAGONFIRE</v>
       </c>
       <c r="C14" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D14" t="str">
-        <v>Kalana gawesh</v>
+        <v>Kanishka Kisal</v>
       </c>
       <c r="E14" t="str">
-        <v>KLNGr</v>
+        <v>Caraxes</v>
       </c>
       <c r="F14" t="str">
-        <v>kalanag.6714@gmail.com</v>
+        <v>kanishkakisaldhanawardana@gmail.com</v>
       </c>
       <c r="G14" t="str">
-        <v>+94769920624</v>
+        <v>+94710938105</v>
       </c>
       <c r="H14" t="str">
         <v>—</v>
@@ -1352,22 +1452,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Hithuwakkarayo</v>
+        <v>DRAGONFIRE</v>
       </c>
       <c r="C15" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D15" t="str">
-        <v>Sadeesh Matheesha</v>
+        <v>Mihindu Udayakanha</v>
       </c>
       <c r="E15" t="str">
-        <v>Sadhiya</v>
+        <v>Vhagar</v>
       </c>
       <c r="F15" t="str">
-        <v>Sadeeshmatheesha@gmail.com</v>
+        <v>mihinduuayakanha0404@gmail.com</v>
       </c>
       <c r="G15" t="str">
-        <v>+94775262450</v>
+        <v>+94714088850</v>
       </c>
       <c r="H15" t="str">
         <v>—</v>
@@ -1381,22 +1481,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Hithuwakkarayo</v>
+        <v>DRAGONFIRE</v>
       </c>
       <c r="C16" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D16" t="str">
-        <v>Wenura Kithmal</v>
+        <v>Shaminda hettiarachchi</v>
       </c>
       <c r="E16" t="str">
-        <v>WKM</v>
+        <v>Cannibal</v>
       </c>
       <c r="F16" t="str">
-        <v>wenura015@gmail.com</v>
+        <v>shamindashaminda66@gmail.com</v>
       </c>
       <c r="G16" t="str">
-        <v>+94716016557</v>
+        <v>+94077398991</v>
       </c>
       <c r="H16" t="str">
         <v>—</v>
@@ -1410,22 +1510,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Hithuwakkarayo</v>
+        <v>DRAGONFIRE</v>
       </c>
       <c r="C17" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D17" t="str">
-        <v>Achintha Gamage</v>
+        <v>Suneth Gevindu</v>
       </c>
       <c r="E17" t="str">
-        <v>ClashMaster</v>
+        <v>NIGHTFURY</v>
       </c>
       <c r="F17" t="str">
-        <v>achinthadineth43@gmail.com</v>
+        <v>gevindusuneth@gmail.com</v>
       </c>
       <c r="G17" t="str">
-        <v>+94712831585</v>
+        <v>+94771520870</v>
       </c>
       <c r="H17" t="str">
         <v>—</v>
@@ -1439,22 +1539,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Team Vnix</v>
+        <v>Ghost Unit</v>
       </c>
       <c r="C18" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D18" t="str">
-        <v>Himeth Iddamalgoda</v>
+        <v>Janith Imalsha</v>
       </c>
       <c r="E18" t="str">
-        <v>VnixKing</v>
+        <v>Dark_Knight</v>
       </c>
       <c r="F18" t="str">
-        <v>24hmalketh2005@gmail.com</v>
+        <v>janithimalsha34@gmail.com</v>
       </c>
       <c r="G18" t="str">
-        <v>+94761605740</v>
+        <v>+94712248323</v>
       </c>
       <c r="H18" t="str">
         <v>—</v>
@@ -1468,22 +1568,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Team Vnix</v>
+        <v>Ghost Unit</v>
       </c>
       <c r="C19" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D19" t="str">
-        <v>Chamithu Bimansith</v>
+        <v>Adithya Prabhashwara</v>
       </c>
       <c r="E19" t="str">
-        <v>VnixBim</v>
+        <v>Dark_Fury</v>
       </c>
       <c r="F19" t="str">
-        <v>chamithuwickramarathna@gmail.com</v>
+        <v>adithyaprabhashwaraADI@gmail.com</v>
       </c>
       <c r="G19" t="str">
-        <v>+94778616099</v>
+        <v>+94713582875</v>
       </c>
       <c r="H19" t="str">
         <v>—</v>
@@ -1497,22 +1597,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Team Vnix</v>
+        <v>Ghost Unit</v>
       </c>
       <c r="C20" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D20" t="str">
-        <v>Sasindu Nimsara</v>
+        <v>Thilina Prabhath</v>
       </c>
       <c r="E20" t="str">
-        <v>VnixDragon</v>
+        <v>Dark_Moon</v>
       </c>
       <c r="F20" t="str">
-        <v>Sasindun790@gmail.com</v>
+        <v>prabhathsriguruge@gmail.com</v>
       </c>
       <c r="G20" t="str">
-        <v>+94788215820</v>
+        <v>+94778487612</v>
       </c>
       <c r="H20" t="str">
         <v>—</v>
@@ -1526,22 +1626,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Team Vnix</v>
+        <v>Ghost Unit</v>
       </c>
       <c r="C21" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D21" t="str">
-        <v>Ravindu weerasekara</v>
+        <v>Dineth Thilanka</v>
       </c>
       <c r="E21" t="str">
-        <v>VnixRaviya</v>
+        <v>Dark_Soul</v>
       </c>
       <c r="F21" t="str">
-        <v>cricmatchbook93@gmail.com</v>
+        <v>dineththilanka2500@gmail.com</v>
       </c>
       <c r="G21" t="str">
-        <v>+94775721981</v>
+        <v>+94705252514</v>
       </c>
       <c r="H21" t="str">
         <v>—</v>
@@ -1555,22 +1655,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Little Princess</v>
+        <v>ShadowX</v>
       </c>
       <c r="C22" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D22" t="str">
-        <v>Thisanga sandin</v>
+        <v>Ranasinghe Jayathri Nameetha</v>
       </c>
       <c r="E22" t="str">
-        <v>Thisanga</v>
+        <v>One Tap</v>
       </c>
       <c r="F22" t="str">
-        <v>thisanga05@gmail.com</v>
+        <v>Ranasranasinghejayathri7@gmail.com</v>
       </c>
       <c r="G22" t="str">
-        <v>+94078545522</v>
+        <v>+94071152716</v>
       </c>
       <c r="H22" t="str">
         <v>—</v>
@@ -1584,22 +1684,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Little Princess</v>
+        <v>ShadowX</v>
       </c>
       <c r="C23" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D23" t="str">
-        <v>Tharuka Devinda</v>
+        <v>R.M.Tharani Chathurya Rathnayaka</v>
       </c>
       <c r="E23" t="str">
-        <v>Flow boyy</v>
+        <v>Deeva</v>
       </c>
       <c r="F23" t="str">
-        <v>zyghorm@gmail.com</v>
+        <v>tharanichathurya9@gmail.com</v>
       </c>
       <c r="G23" t="str">
-        <v>+94753565268</v>
+        <v>+94761285825</v>
       </c>
       <c r="H23" t="str">
         <v>—</v>
@@ -1613,22 +1713,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Little Princess</v>
+        <v>ShadowX</v>
       </c>
       <c r="C24" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D24" t="str">
-        <v>Damidu Herath</v>
+        <v xml:space="preserve">Shashmila Laknadi </v>
       </c>
       <c r="E24" t="str">
-        <v>Damiduuu</v>
+        <v>Zia</v>
       </c>
       <c r="F24" t="str">
-        <v>damiduherath@gmail.com</v>
+        <v>shashmilalaknadi24@gmail.com</v>
       </c>
       <c r="G24" t="str">
-        <v>+94774850925</v>
+        <v>+94784201134</v>
       </c>
       <c r="H24" t="str">
         <v>—</v>
@@ -1642,22 +1742,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Little Princess</v>
+        <v>ShadowX</v>
       </c>
       <c r="C25" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D25" t="str">
-        <v>Dinal Akash</v>
+        <v>Subenthiran Kajani</v>
       </c>
       <c r="E25" t="str">
-        <v>Dinall</v>
+        <v>Zena</v>
       </c>
       <c r="F25" t="str">
-        <v>randeshdaluwatte@gmail.com</v>
+        <v>subenthirankajani35@gmail.com</v>
       </c>
       <c r="G25" t="str">
-        <v>+94754887389</v>
+        <v>+94719170183</v>
       </c>
       <c r="H25" t="str">
         <v>—</v>
@@ -1671,25 +1771,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Phantom Squad</v>
+        <v>Hithuwakkarayo</v>
       </c>
       <c r="C26" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D26" t="str">
-        <v>Rizmiya Rajabdeen</v>
+        <v>Kalana gawesh</v>
       </c>
       <c r="E26" t="str">
-        <v>RushQueen</v>
+        <v>KLNGr</v>
       </c>
       <c r="F26" t="str">
-        <v>rizmiyarajabdeen@gmail.com</v>
+        <v>kalanag.6714@gmail.com</v>
       </c>
       <c r="G26" t="str">
-        <v>+94768880741</v>
+        <v>+94769920624</v>
       </c>
       <c r="H26" t="str">
-        <v>IM/2024/026</v>
+        <v>—</v>
       </c>
       <c r="I26" t="str">
         <v>Main Roster</v>
@@ -1700,25 +1800,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Phantom Squad</v>
+        <v>Hithuwakkarayo</v>
       </c>
       <c r="C27" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D27" t="str">
-        <v>Bosadi Kothalawala</v>
+        <v>Sadeesh Matheesha</v>
       </c>
       <c r="E27" t="str">
-        <v>Luna</v>
+        <v>Sadhiya</v>
       </c>
       <c r="F27" t="str">
-        <v>bosadithimansha@gmail.com</v>
+        <v>Sadeeshmatheesha@gmail.com</v>
       </c>
       <c r="G27" t="str">
-        <v>+94772564147</v>
+        <v>+94775262450</v>
       </c>
       <c r="H27" t="str">
-        <v>IM/2023/140</v>
+        <v>—</v>
       </c>
       <c r="I27" t="str">
         <v>Main Roster</v>
@@ -1729,25 +1829,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Phantom Squad</v>
+        <v>Hithuwakkarayo</v>
       </c>
       <c r="C28" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D28" t="str">
-        <v>Navindi Thisarani</v>
+        <v>Wenura Kithmal</v>
       </c>
       <c r="E28" t="str">
-        <v>CodCat</v>
+        <v>WKM</v>
       </c>
       <c r="F28" t="str">
-        <v>navindithisarani17@gmail.com</v>
+        <v>wenura015@gmail.com</v>
       </c>
       <c r="G28" t="str">
-        <v>+94771452859</v>
+        <v>+94716016557</v>
       </c>
       <c r="H28" t="str">
-        <v>IM/2024/040</v>
+        <v>—</v>
       </c>
       <c r="I28" t="str">
         <v>Main Roster</v>
@@ -1758,25 +1858,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Phantom Squad</v>
+        <v>Hithuwakkarayo</v>
       </c>
       <c r="C29" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D29" t="str">
-        <v>Thisasni Damsiluni</v>
+        <v>Achintha Gamage</v>
       </c>
       <c r="E29" t="str">
-        <v>Twilight</v>
+        <v>ClashMaster</v>
       </c>
       <c r="F29" t="str">
-        <v>foreveryoungthisa@gmail.com</v>
+        <v>achinthadineth43@gmail.com</v>
       </c>
       <c r="G29" t="str">
-        <v>+94712484211</v>
+        <v>+94712831585</v>
       </c>
       <c r="H29" t="str">
-        <v>IM/2024/066</v>
+        <v>—</v>
       </c>
       <c r="I29" t="str">
         <v>Main Roster</v>
@@ -1787,22 +1887,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>VEX</v>
+        <v>Team Vnix</v>
       </c>
       <c r="C30" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D30" t="str">
-        <v>THUSHANTH</v>
+        <v>Himeth Iddamalgoda</v>
       </c>
       <c r="E30" t="str">
-        <v>Thushanth</v>
+        <v>VnixKing</v>
       </c>
       <c r="F30" t="str">
-        <v>chandranthushanth@gmail.com</v>
+        <v>24hmalketh2005@gmail.com</v>
       </c>
       <c r="G30" t="str">
-        <v>+94773328937</v>
+        <v>+94761605740</v>
       </c>
       <c r="H30" t="str">
         <v>—</v>
@@ -1816,22 +1916,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>VEX</v>
+        <v>Team Vnix</v>
       </c>
       <c r="C31" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D31" t="str">
-        <v>RIZNY</v>
+        <v>Chamithu Bimansith</v>
       </c>
       <c r="E31" t="str">
-        <v>Rizee</v>
+        <v>VnixBim</v>
       </c>
       <c r="F31" t="str">
-        <v>mohamedrizee2005@gmail.com</v>
+        <v>chamithuwickramarathna@gmail.com</v>
       </c>
       <c r="G31" t="str">
-        <v>+94756166103</v>
+        <v>+94778616099</v>
       </c>
       <c r="H31" t="str">
         <v>—</v>
@@ -1845,22 +1945,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>VEX</v>
+        <v>Team Vnix</v>
       </c>
       <c r="C32" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D32" t="str">
-        <v>Kaveesha Fernando</v>
+        <v>Sasindu Nimsara</v>
       </c>
       <c r="E32" t="str">
-        <v>Jayden_Roy05</v>
+        <v>VnixDragon</v>
       </c>
       <c r="F32" t="str">
-        <v>kaveeshaf12@gmail.com</v>
+        <v>Sasindun790@gmail.com</v>
       </c>
       <c r="G32" t="str">
-        <v>+94718685596</v>
+        <v>+94788215820</v>
       </c>
       <c r="H32" t="str">
         <v>—</v>
@@ -1874,22 +1974,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>VEX</v>
+        <v>Team Vnix</v>
       </c>
       <c r="C33" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D33" t="str">
-        <v>Indusara Rathnayake</v>
+        <v>Ravindu weerasekara</v>
       </c>
       <c r="E33" t="str">
-        <v>Zara_69</v>
+        <v>VnixRaviya</v>
       </c>
       <c r="F33" t="str">
-        <v>induzara69@gmail.com</v>
+        <v>cricmatchbook93@gmail.com</v>
       </c>
       <c r="G33" t="str">
-        <v>+94719944136</v>
+        <v>+94775721981</v>
       </c>
       <c r="H33" t="str">
         <v>—</v>
@@ -1903,25 +2003,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>The Annabelles</v>
+        <v>Little Princess</v>
       </c>
       <c r="C34" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D34" t="str">
-        <v>R.P.S.A.Keshani</v>
+        <v>Thisanga sandin</v>
       </c>
       <c r="E34" t="str">
-        <v>Zeraphy</v>
+        <v>Thisanga</v>
       </c>
       <c r="F34" t="str">
-        <v>sanduniamasha876@gmail.com</v>
+        <v>thisanga05@gmail.com</v>
       </c>
       <c r="G34" t="str">
-        <v>+94076066765</v>
+        <v>+94078545522</v>
       </c>
       <c r="H34" t="str">
-        <v>IM/2024/045</v>
+        <v>—</v>
       </c>
       <c r="I34" t="str">
         <v>Main Roster</v>
@@ -1932,25 +2032,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>The Annabelles</v>
+        <v>Little Princess</v>
       </c>
       <c r="C35" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D35" t="str">
-        <v>D.Sandima Umayanjalee</v>
+        <v>Tharuka Devinda</v>
       </c>
       <c r="E35" t="str">
-        <v>Roxyfire</v>
+        <v>Flow boyy</v>
       </c>
       <c r="F35" t="str">
-        <v>sandimaumayanjalee2005@gmail.com</v>
+        <v>zyghorm@gmail.com</v>
       </c>
       <c r="G35" t="str">
-        <v>+94721469871</v>
+        <v>+94753565268</v>
       </c>
       <c r="H35" t="str">
-        <v>IM/2024/041</v>
+        <v>—</v>
       </c>
       <c r="I35" t="str">
         <v>Main Roster</v>
@@ -1961,25 +2061,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>The Annabelles</v>
+        <v>Little Princess</v>
       </c>
       <c r="C36" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D36" t="str">
-        <v>Yashmi Amadi</v>
+        <v>Damidu Herath</v>
       </c>
       <c r="E36" t="str">
-        <v>Andromeda</v>
+        <v>Damiduuu</v>
       </c>
       <c r="F36" t="str">
-        <v>yashamax555@gmail.com</v>
+        <v>damiduherath@gmail.com</v>
       </c>
       <c r="G36" t="str">
-        <v>+94077856852</v>
+        <v>+94774850925</v>
       </c>
       <c r="H36" t="str">
-        <v>IM/2024/059</v>
+        <v>—</v>
       </c>
       <c r="I36" t="str">
         <v>Main Roster</v>
@@ -1990,40 +2090,272 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>The Annabelles</v>
+        <v>Little Princess</v>
       </c>
       <c r="C37" t="str">
         <v>APPROVED</v>
       </c>
       <c r="D37" t="str">
-        <v>D.M.V.I.Dissanayake</v>
+        <v>Dinal Akash</v>
       </c>
       <c r="E37" t="str">
-        <v>vortex</v>
+        <v>Dinall</v>
       </c>
       <c r="F37" t="str">
-        <v>vishmi.dissanayake1122@gmail.com</v>
+        <v>randeshdaluwatte@gmail.com</v>
       </c>
       <c r="G37" t="str">
-        <v>+94788943505</v>
+        <v>+94754887389</v>
       </c>
       <c r="H37" t="str">
-        <v>IM/2024/083</v>
+        <v>—</v>
       </c>
       <c r="I37" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Phantom Squad</v>
+      </c>
+      <c r="C38" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Rizmiya Rajabdeen</v>
+      </c>
+      <c r="E38" t="str">
+        <v>RushQueen</v>
+      </c>
+      <c r="F38" t="str">
+        <v>rizmiyarajabdeen@gmail.com</v>
+      </c>
+      <c r="G38" t="str">
+        <v>+94768880741</v>
+      </c>
+      <c r="H38" t="str">
+        <v>IM/2024/026</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Phantom Squad</v>
+      </c>
+      <c r="C39" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Bosadi Kothalawala</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Luna</v>
+      </c>
+      <c r="F39" t="str">
+        <v>bosadithimansha@gmail.com</v>
+      </c>
+      <c r="G39" t="str">
+        <v>+94772564147</v>
+      </c>
+      <c r="H39" t="str">
+        <v>IM/2023/140</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Phantom Squad</v>
+      </c>
+      <c r="C40" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Navindi Thisarani</v>
+      </c>
+      <c r="E40" t="str">
+        <v>CodCat</v>
+      </c>
+      <c r="F40" t="str">
+        <v>navindithisarani17@gmail.com</v>
+      </c>
+      <c r="G40" t="str">
+        <v>+94771452859</v>
+      </c>
+      <c r="H40" t="str">
+        <v>IM/2024/040</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Phantom Squad</v>
+      </c>
+      <c r="C41" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Thisasni Damsiluni</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Twilight</v>
+      </c>
+      <c r="F41" t="str">
+        <v>foreveryoungthisa@gmail.com</v>
+      </c>
+      <c r="G41" t="str">
+        <v>+94712484211</v>
+      </c>
+      <c r="H41" t="str">
+        <v>IM/2024/066</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>VEX</v>
+      </c>
+      <c r="C42" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D42" t="str">
+        <v>THUSHANTH</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Thushanth</v>
+      </c>
+      <c r="F42" t="str">
+        <v>chandranthushanth@gmail.com</v>
+      </c>
+      <c r="G42" t="str">
+        <v>+94773328937</v>
+      </c>
+      <c r="H42" t="str">
+        <v>—</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>VEX</v>
+      </c>
+      <c r="C43" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D43" t="str">
+        <v>RIZNY</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Rizee</v>
+      </c>
+      <c r="F43" t="str">
+        <v>mohamedrizee2005@gmail.com</v>
+      </c>
+      <c r="G43" t="str">
+        <v>+94756166103</v>
+      </c>
+      <c r="H43" t="str">
+        <v>—</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>VEX</v>
+      </c>
+      <c r="C44" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Kaveesha Fernando</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Jayden_Roy05</v>
+      </c>
+      <c r="F44" t="str">
+        <v>kaveeshaf12@gmail.com</v>
+      </c>
+      <c r="G44" t="str">
+        <v>+94718685596</v>
+      </c>
+      <c r="H44" t="str">
+        <v>—</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>VEX</v>
+      </c>
+      <c r="C45" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Indusara Rathnayake</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Zara_69</v>
+      </c>
+      <c r="F45" t="str">
+        <v>induzara69@gmail.com</v>
+      </c>
+      <c r="G45" t="str">
+        <v>+94719944136</v>
+      </c>
+      <c r="H45" t="str">
+        <v>—</v>
+      </c>
+      <c r="I45" t="str">
         <v>Main Roster</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I67"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2067,16 +2399,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TEAM: DRAGONFIRE</v>
+        <v>TEAM: ROSA KEKULU A</v>
       </c>
       <c r="B2" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C2" t="str">
-        <v>Kasun Lakshan (unikasun55@gmail.com)</v>
+        <v>Navida Sandiv Gamage (navidasandiv@gmail.com)</v>
       </c>
       <c r="D2" t="str">
-        <v>+94704180640</v>
+        <v>+94718833133</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -2108,16 +2440,16 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>1. Kanishka Kisal</v>
+        <v>1. Sithum Adhikaranayake</v>
       </c>
       <c r="F3" t="str">
-        <v>Caraxes</v>
+        <v>KIVIER</v>
       </c>
       <c r="G3" t="str">
-        <v>kanishkakisaldhanawardana@gmail.com</v>
+        <v>itsnotsithum@gmail.com</v>
       </c>
       <c r="H3" t="str">
-        <v>+94710938105</v>
+        <v>+94714018738</v>
       </c>
       <c r="I3" t="str">
         <v>Main Roster</v>
@@ -2137,16 +2469,16 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>2. Mihindu Udayakanha</v>
+        <v>2. Pasindu Ruwanpathirana</v>
       </c>
       <c r="F4" t="str">
-        <v>Vhagar</v>
+        <v>Scalesteep</v>
       </c>
       <c r="G4" t="str">
-        <v>mihinduuayakanha0404@gmail.com</v>
+        <v>bimsarapasindurp@gmail.com</v>
       </c>
       <c r="H4" t="str">
-        <v>+94714088850</v>
+        <v>+94715726416</v>
       </c>
       <c r="I4" t="str">
         <v>Main Roster</v>
@@ -2166,16 +2498,16 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>3. Shaminda hettiarachchi</v>
+        <v>3. Luchitha Navaratne</v>
       </c>
       <c r="F5" t="str">
-        <v>Cannibal</v>
+        <v>luvia</v>
       </c>
       <c r="G5" t="str">
-        <v>shamindashaminda66@gmail.com</v>
+        <v>lonathluchitha@gmail.com</v>
       </c>
       <c r="H5" t="str">
-        <v>+94077398991</v>
+        <v>+94706680588</v>
       </c>
       <c r="I5" t="str">
         <v>Main Roster</v>
@@ -2195,16 +2527,16 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>4. Suneth Gevindu</v>
+        <v>4. Shehan Nimsara</v>
       </c>
       <c r="F6" t="str">
-        <v>NIGHTFURY</v>
+        <v>Aizen</v>
       </c>
       <c r="G6" t="str">
-        <v>gevindusuneth@gmail.com</v>
+        <v>shehannimsara@gmail.com</v>
       </c>
       <c r="H6" t="str">
-        <v>+94771520870</v>
+        <v>+94783890996</v>
       </c>
       <c r="I6" t="str">
         <v>Main Roster</v>
@@ -2241,16 +2573,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TEAM: GHOST UNIT</v>
+        <v>TEAM: ROSA KEKULU B</v>
       </c>
       <c r="B8" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C8" t="str">
-        <v>Thilina Ravishan (thilinaravishan2003@gmail.com)</v>
+        <v>Savindu mihiran (savindumihiran12345@gmail.com)</v>
       </c>
       <c r="D8" t="str">
-        <v>+94767852670</v>
+        <v>+94762934155</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -2282,16 +2614,16 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>1. Janith Imalsha</v>
+        <v>1. A.S.Tharu Gimhana silva</v>
       </c>
       <c r="F9" t="str">
-        <v>Dark_Knight</v>
+        <v>StarLord</v>
       </c>
       <c r="G9" t="str">
-        <v>janithimalsha34@gmail.com</v>
+        <v>shehantharu2095@gmail.com</v>
       </c>
       <c r="H9" t="str">
-        <v>+94712248323</v>
+        <v>+94712302182</v>
       </c>
       <c r="I9" t="str">
         <v>Main Roster</v>
@@ -2311,16 +2643,16 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>2. Adithya Prabhashwara</v>
+        <v>2. L.P Kaveen Roshana Liyanapathirana</v>
       </c>
       <c r="F10" t="str">
-        <v>Dark_Fury</v>
+        <v>Zyren</v>
       </c>
       <c r="G10" t="str">
-        <v>adithyaprabhashwaraADI@gmail.com</v>
+        <v>kaveen.roshana@gmail.com</v>
       </c>
       <c r="H10" t="str">
-        <v>+94713582875</v>
+        <v>+94762862215</v>
       </c>
       <c r="I10" t="str">
         <v>Main Roster</v>
@@ -2340,16 +2672,16 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>3. Thilina Prabhath</v>
+        <v>3. Thinuga Sesanda</v>
       </c>
       <c r="F11" t="str">
-        <v>Dark_Moon</v>
+        <v>TeraX</v>
       </c>
       <c r="G11" t="str">
-        <v>prabhathsriguruge@gmail.com</v>
+        <v>thinugasesanda2005@gmail.com</v>
       </c>
       <c r="H11" t="str">
-        <v>+94778487612</v>
+        <v>+94712052080</v>
       </c>
       <c r="I11" t="str">
         <v>Main Roster</v>
@@ -2369,16 +2701,16 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>4. Dineth Thilanka</v>
+        <v>4. S.L.K. Prabhashana</v>
       </c>
       <c r="F12" t="str">
-        <v>Dark_Soul</v>
+        <v>Kingslayer</v>
       </c>
       <c r="G12" t="str">
-        <v>dineththilanka2500@gmail.com</v>
+        <v>slkprabhashana@gmail.com</v>
       </c>
       <c r="H12" t="str">
-        <v>+94705252514</v>
+        <v>+94719567174</v>
       </c>
       <c r="I12" t="str">
         <v>Main Roster</v>
@@ -2415,16 +2747,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TEAM: SHADOWX</v>
+        <v>TEAM: THE ANNABELLES</v>
       </c>
       <c r="B14" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C14" t="str">
-        <v>Thathsarani Thenujana  (thathsaranithenujana@gmail.com)</v>
+        <v>leader (induminipabasara1@gmail.com)</v>
       </c>
       <c r="D14" t="str">
-        <v>+94785600006</v>
+        <v>+94704897405</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -2456,16 +2788,16 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>1. Ranasinghe Jayathri Nameetha</v>
+        <v>1. R.P.S.A.Keshani</v>
       </c>
       <c r="F15" t="str">
-        <v>One Tap</v>
+        <v>Zeraphy</v>
       </c>
       <c r="G15" t="str">
-        <v>Ranasranasinghejayathri7@gmail.com</v>
+        <v>sanduniamasha876@gmail.com</v>
       </c>
       <c r="H15" t="str">
-        <v>+94071152716</v>
+        <v>+94760667655</v>
       </c>
       <c r="I15" t="str">
         <v>Main Roster</v>
@@ -2485,16 +2817,16 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>2. R.M.Tharani Chathurya Rathnayaka</v>
+        <v>2. Dewage Sandima Umayanjalee De Silva</v>
       </c>
       <c r="F16" t="str">
-        <v>Deeva</v>
+        <v>RoxyFire</v>
       </c>
       <c r="G16" t="str">
-        <v>tharanichathurya9@gmail.com</v>
+        <v>sandimaumayanjalee2005@gmail.com</v>
       </c>
       <c r="H16" t="str">
-        <v>+94761285825</v>
+        <v>+94721469871</v>
       </c>
       <c r="I16" t="str">
         <v>Main Roster</v>
@@ -2514,16 +2846,16 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v xml:space="preserve">3. Shashmila Laknadi </v>
+        <v>3. D M V I Dissanayake</v>
       </c>
       <c r="F17" t="str">
-        <v>Zia</v>
+        <v>Vortex</v>
       </c>
       <c r="G17" t="str">
-        <v>shashmilalaknadi24@gmail.com</v>
+        <v>vishmi.dissanayake1122@gmail.com</v>
       </c>
       <c r="H17" t="str">
-        <v>+94784201134</v>
+        <v>+94788943505</v>
       </c>
       <c r="I17" t="str">
         <v>Main Roster</v>
@@ -2543,16 +2875,16 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>4. Subenthiran Kajani</v>
+        <v>4. Yashmi Amadhi Rajapakse</v>
       </c>
       <c r="F18" t="str">
-        <v>Zena</v>
+        <v>Andromeda</v>
       </c>
       <c r="G18" t="str">
-        <v>subenthirankajani35@gmail.com</v>
+        <v>yashamax555@gmail.com</v>
       </c>
       <c r="H18" t="str">
-        <v>+94719170183</v>
+        <v>+94778568529</v>
       </c>
       <c r="I18" t="str">
         <v>Main Roster</v>
@@ -2589,16 +2921,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TEAM: HITHUWAKKARAYO</v>
+        <v>TEAM: DRAGONFIRE</v>
       </c>
       <c r="B20" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C20" t="str">
-        <v>Harsha madhubashana  (subash11246@gmail.com)</v>
+        <v>Kasun Lakshan (unikasun55@gmail.com)</v>
       </c>
       <c r="D20" t="str">
-        <v>+94721508452</v>
+        <v>+94704180640</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -2630,16 +2962,16 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>1. Kalana gawesh</v>
+        <v>1. Kanishka Kisal</v>
       </c>
       <c r="F21" t="str">
-        <v>KLNGr</v>
+        <v>Caraxes</v>
       </c>
       <c r="G21" t="str">
-        <v>kalanag.6714@gmail.com</v>
+        <v>kanishkakisaldhanawardana@gmail.com</v>
       </c>
       <c r="H21" t="str">
-        <v>+94769920624</v>
+        <v>+94710938105</v>
       </c>
       <c r="I21" t="str">
         <v>Main Roster</v>
@@ -2659,16 +2991,16 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>2. Sadeesh Matheesha</v>
+        <v>2. Mihindu Udayakanha</v>
       </c>
       <c r="F22" t="str">
-        <v>Sadhiya</v>
+        <v>Vhagar</v>
       </c>
       <c r="G22" t="str">
-        <v>Sadeeshmatheesha@gmail.com</v>
+        <v>mihinduuayakanha0404@gmail.com</v>
       </c>
       <c r="H22" t="str">
-        <v>+94775262450</v>
+        <v>+94714088850</v>
       </c>
       <c r="I22" t="str">
         <v>Main Roster</v>
@@ -2688,16 +3020,16 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>3. Wenura Kithmal</v>
+        <v>3. Shaminda hettiarachchi</v>
       </c>
       <c r="F23" t="str">
-        <v>WKM</v>
+        <v>Cannibal</v>
       </c>
       <c r="G23" t="str">
-        <v>wenura015@gmail.com</v>
+        <v>shamindashaminda66@gmail.com</v>
       </c>
       <c r="H23" t="str">
-        <v>+94716016557</v>
+        <v>+94077398991</v>
       </c>
       <c r="I23" t="str">
         <v>Main Roster</v>
@@ -2717,16 +3049,16 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>4. Achintha Gamage</v>
+        <v>4. Suneth Gevindu</v>
       </c>
       <c r="F24" t="str">
-        <v>ClashMaster</v>
+        <v>NIGHTFURY</v>
       </c>
       <c r="G24" t="str">
-        <v>achinthadineth43@gmail.com</v>
+        <v>gevindusuneth@gmail.com</v>
       </c>
       <c r="H24" t="str">
-        <v>+94712831585</v>
+        <v>+94771520870</v>
       </c>
       <c r="I24" t="str">
         <v>Main Roster</v>
@@ -2763,16 +3095,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TEAM: TEAM VNIX</v>
+        <v>TEAM: GHOST UNIT</v>
       </c>
       <c r="B26" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C26" t="str">
-        <v>Naveen Hiranya (naveenhiranya999@gmail.com)</v>
+        <v>Thilina Ravishan (thilinaravishan2003@gmail.com)</v>
       </c>
       <c r="D26" t="str">
-        <v>+94756067029</v>
+        <v>+94767852670</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -2804,16 +3136,16 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>1. Himeth Iddamalgoda</v>
+        <v>1. Janith Imalsha</v>
       </c>
       <c r="F27" t="str">
-        <v>VnixKing</v>
+        <v>Dark_Knight</v>
       </c>
       <c r="G27" t="str">
-        <v>24hmalketh2005@gmail.com</v>
+        <v>janithimalsha34@gmail.com</v>
       </c>
       <c r="H27" t="str">
-        <v>+94761605740</v>
+        <v>+94712248323</v>
       </c>
       <c r="I27" t="str">
         <v>Main Roster</v>
@@ -2833,16 +3165,16 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>2. Chamithu Bimansith</v>
+        <v>2. Adithya Prabhashwara</v>
       </c>
       <c r="F28" t="str">
-        <v>VnixBim</v>
+        <v>Dark_Fury</v>
       </c>
       <c r="G28" t="str">
-        <v>chamithuwickramarathna@gmail.com</v>
+        <v>adithyaprabhashwaraADI@gmail.com</v>
       </c>
       <c r="H28" t="str">
-        <v>+94778616099</v>
+        <v>+94713582875</v>
       </c>
       <c r="I28" t="str">
         <v>Main Roster</v>
@@ -2862,16 +3194,16 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>3. Sasindu Nimsara</v>
+        <v>3. Thilina Prabhath</v>
       </c>
       <c r="F29" t="str">
-        <v>VnixDragon</v>
+        <v>Dark_Moon</v>
       </c>
       <c r="G29" t="str">
-        <v>Sasindun790@gmail.com</v>
+        <v>prabhathsriguruge@gmail.com</v>
       </c>
       <c r="H29" t="str">
-        <v>+94788215820</v>
+        <v>+94778487612</v>
       </c>
       <c r="I29" t="str">
         <v>Main Roster</v>
@@ -2891,16 +3223,16 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>4. Ravindu weerasekara</v>
+        <v>4. Dineth Thilanka</v>
       </c>
       <c r="F30" t="str">
-        <v>VnixRaviya</v>
+        <v>Dark_Soul</v>
       </c>
       <c r="G30" t="str">
-        <v>cricmatchbook93@gmail.com</v>
+        <v>dineththilanka2500@gmail.com</v>
       </c>
       <c r="H30" t="str">
-        <v>+94775721981</v>
+        <v>+94705252514</v>
       </c>
       <c r="I30" t="str">
         <v>Main Roster</v>
@@ -2937,16 +3269,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TEAM: LITTLE PRINCESS</v>
+        <v>TEAM: SHADOWX</v>
       </c>
       <c r="B32" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C32" t="str">
-        <v>Randesh Daluwatte (randesh123@gmail.com)</v>
+        <v>Thathsarani Thenujana  (thathsaranithenujana@gmail.com)</v>
       </c>
       <c r="D32" t="str">
-        <v>+94775671929</v>
+        <v>+94785600006</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -2978,16 +3310,16 @@
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>1. Thisanga sandin</v>
+        <v>1. Ranasinghe Jayathri Nameetha</v>
       </c>
       <c r="F33" t="str">
-        <v>Thisanga</v>
+        <v>One Tap</v>
       </c>
       <c r="G33" t="str">
-        <v>thisanga05@gmail.com</v>
+        <v>Ranasranasinghejayathri7@gmail.com</v>
       </c>
       <c r="H33" t="str">
-        <v>+94078545522</v>
+        <v>+94071152716</v>
       </c>
       <c r="I33" t="str">
         <v>Main Roster</v>
@@ -3007,16 +3339,16 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>2. Tharuka Devinda</v>
+        <v>2. R.M.Tharani Chathurya Rathnayaka</v>
       </c>
       <c r="F34" t="str">
-        <v>Flow boyy</v>
+        <v>Deeva</v>
       </c>
       <c r="G34" t="str">
-        <v>zyghorm@gmail.com</v>
+        <v>tharanichathurya9@gmail.com</v>
       </c>
       <c r="H34" t="str">
-        <v>+94753565268</v>
+        <v>+94761285825</v>
       </c>
       <c r="I34" t="str">
         <v>Main Roster</v>
@@ -3036,16 +3368,16 @@
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>3. Damidu Herath</v>
+        <v xml:space="preserve">3. Shashmila Laknadi </v>
       </c>
       <c r="F35" t="str">
-        <v>Damiduuu</v>
+        <v>Zia</v>
       </c>
       <c r="G35" t="str">
-        <v>damiduherath@gmail.com</v>
+        <v>shashmilalaknadi24@gmail.com</v>
       </c>
       <c r="H35" t="str">
-        <v>+94774850925</v>
+        <v>+94784201134</v>
       </c>
       <c r="I35" t="str">
         <v>Main Roster</v>
@@ -3065,16 +3397,16 @@
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>4. Dinal Akash</v>
+        <v>4. Subenthiran Kajani</v>
       </c>
       <c r="F36" t="str">
-        <v>Dinall</v>
+        <v>Zena</v>
       </c>
       <c r="G36" t="str">
-        <v>randeshdaluwatte@gmail.com</v>
+        <v>subenthirankajani35@gmail.com</v>
       </c>
       <c r="H36" t="str">
-        <v>+94754887389</v>
+        <v>+94719170183</v>
       </c>
       <c r="I36" t="str">
         <v>Main Roster</v>
@@ -3111,16 +3443,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TEAM: PHANTOM SQUAD</v>
+        <v>TEAM: HITHUWAKKARAYO</v>
       </c>
       <c r="B38" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C38" t="str">
-        <v>Sudhari Rajakaruna (sudharirajakaruna2005@gmail.com)</v>
+        <v>Harsha madhubashana  (subash11246@gmail.com)</v>
       </c>
       <c r="D38" t="str">
-        <v>+94777531210</v>
+        <v>+94721508452</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -3152,16 +3484,16 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>1. Rizmiya Rajabdeen</v>
+        <v>1. Kalana gawesh</v>
       </c>
       <c r="F39" t="str">
-        <v>RushQueen</v>
+        <v>KLNGr</v>
       </c>
       <c r="G39" t="str">
-        <v>rizmiyarajabdeen@gmail.com</v>
+        <v>kalanag.6714@gmail.com</v>
       </c>
       <c r="H39" t="str">
-        <v>+94768880741</v>
+        <v>+94769920624</v>
       </c>
       <c r="I39" t="str">
         <v>Main Roster</v>
@@ -3181,16 +3513,16 @@
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>2. Bosadi Kothalawala</v>
+        <v>2. Sadeesh Matheesha</v>
       </c>
       <c r="F40" t="str">
-        <v>Luna</v>
+        <v>Sadhiya</v>
       </c>
       <c r="G40" t="str">
-        <v>bosadithimansha@gmail.com</v>
+        <v>Sadeeshmatheesha@gmail.com</v>
       </c>
       <c r="H40" t="str">
-        <v>+94772564147</v>
+        <v>+94775262450</v>
       </c>
       <c r="I40" t="str">
         <v>Main Roster</v>
@@ -3210,16 +3542,16 @@
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>3. Navindi Thisarani</v>
+        <v>3. Wenura Kithmal</v>
       </c>
       <c r="F41" t="str">
-        <v>CodCat</v>
+        <v>WKM</v>
       </c>
       <c r="G41" t="str">
-        <v>navindithisarani17@gmail.com</v>
+        <v>wenura015@gmail.com</v>
       </c>
       <c r="H41" t="str">
-        <v>+94771452859</v>
+        <v>+94716016557</v>
       </c>
       <c r="I41" t="str">
         <v>Main Roster</v>
@@ -3239,16 +3571,16 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>4. Thisasni Damsiluni</v>
+        <v>4. Achintha Gamage</v>
       </c>
       <c r="F42" t="str">
-        <v>Twilight</v>
+        <v>ClashMaster</v>
       </c>
       <c r="G42" t="str">
-        <v>foreveryoungthisa@gmail.com</v>
+        <v>achinthadineth43@gmail.com</v>
       </c>
       <c r="H42" t="str">
-        <v>+94712484211</v>
+        <v>+94712831585</v>
       </c>
       <c r="I42" t="str">
         <v>Main Roster</v>
@@ -3285,16 +3617,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TEAM: VEX</v>
+        <v>TEAM: TEAM VNIX</v>
       </c>
       <c r="B44" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C44" t="str">
-        <v>JEZAN N (jezanjoy@gmail.com)</v>
+        <v>Naveen Hiranya (naveenhiranya999@gmail.com)</v>
       </c>
       <c r="D44" t="str">
-        <v>+94754860486</v>
+        <v>+94756067029</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -3326,16 +3658,16 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>1. THUSHANTH</v>
+        <v>1. Himeth Iddamalgoda</v>
       </c>
       <c r="F45" t="str">
-        <v>Thushanth</v>
+        <v>VnixKing</v>
       </c>
       <c r="G45" t="str">
-        <v>chandranthushanth@gmail.com</v>
+        <v>24hmalketh2005@gmail.com</v>
       </c>
       <c r="H45" t="str">
-        <v>+94773328937</v>
+        <v>+94761605740</v>
       </c>
       <c r="I45" t="str">
         <v>Main Roster</v>
@@ -3355,16 +3687,16 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>2. RIZNY</v>
+        <v>2. Chamithu Bimansith</v>
       </c>
       <c r="F46" t="str">
-        <v>Rizee</v>
+        <v>VnixBim</v>
       </c>
       <c r="G46" t="str">
-        <v>mohamedrizee2005@gmail.com</v>
+        <v>chamithuwickramarathna@gmail.com</v>
       </c>
       <c r="H46" t="str">
-        <v>+94756166103</v>
+        <v>+94778616099</v>
       </c>
       <c r="I46" t="str">
         <v>Main Roster</v>
@@ -3384,16 +3716,16 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>3. Kaveesha Fernando</v>
+        <v>3. Sasindu Nimsara</v>
       </c>
       <c r="F47" t="str">
-        <v>Jayden_Roy05</v>
+        <v>VnixDragon</v>
       </c>
       <c r="G47" t="str">
-        <v>kaveeshaf12@gmail.com</v>
+        <v>Sasindun790@gmail.com</v>
       </c>
       <c r="H47" t="str">
-        <v>+94718685596</v>
+        <v>+94788215820</v>
       </c>
       <c r="I47" t="str">
         <v>Main Roster</v>
@@ -3413,16 +3745,16 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>4. Indusara Rathnayake</v>
+        <v>4. Ravindu weerasekara</v>
       </c>
       <c r="F48" t="str">
-        <v>Zara_69</v>
+        <v>VnixRaviya</v>
       </c>
       <c r="G48" t="str">
-        <v>induzara69@gmail.com</v>
+        <v>cricmatchbook93@gmail.com</v>
       </c>
       <c r="H48" t="str">
-        <v>+94719944136</v>
+        <v>+94775721981</v>
       </c>
       <c r="I48" t="str">
         <v>Main Roster</v>
@@ -3459,16 +3791,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>TEAM: THE ANNABELLES</v>
+        <v>TEAM: LITTLE PRINCESS</v>
       </c>
       <c r="B50" t="str">
         <v>[ APPROVED ]</v>
       </c>
       <c r="C50" t="str">
-        <v>Kumanayakage pabasara indumini (induminipabasara1@gmail.com)</v>
+        <v>Randesh Daluwatte (randesh123@gmail.com)</v>
       </c>
       <c r="D50" t="str">
-        <v>+94704897405</v>
+        <v>+94775671929</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -3500,16 +3832,16 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>1. R.P.S.A.Keshani</v>
+        <v>1. Thisanga sandin</v>
       </c>
       <c r="F51" t="str">
-        <v>Zeraphy</v>
+        <v>Thisanga</v>
       </c>
       <c r="G51" t="str">
-        <v>sanduniamasha876@gmail.com</v>
+        <v>thisanga05@gmail.com</v>
       </c>
       <c r="H51" t="str">
-        <v>+94076066765</v>
+        <v>+94078545522</v>
       </c>
       <c r="I51" t="str">
         <v>Main Roster</v>
@@ -3529,16 +3861,16 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>2. D.Sandima Umayanjalee</v>
+        <v>2. Tharuka Devinda</v>
       </c>
       <c r="F52" t="str">
-        <v>Roxyfire</v>
+        <v>Flow boyy</v>
       </c>
       <c r="G52" t="str">
-        <v>sandimaumayanjalee2005@gmail.com</v>
+        <v>zyghorm@gmail.com</v>
       </c>
       <c r="H52" t="str">
-        <v>+94721469871</v>
+        <v>+94753565268</v>
       </c>
       <c r="I52" t="str">
         <v>Main Roster</v>
@@ -3558,16 +3890,16 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>3. Yashmi Amadi</v>
+        <v>3. Damidu Herath</v>
       </c>
       <c r="F53" t="str">
-        <v>Andromeda</v>
+        <v>Damiduuu</v>
       </c>
       <c r="G53" t="str">
-        <v>yashamax555@gmail.com</v>
+        <v>damiduherath@gmail.com</v>
       </c>
       <c r="H53" t="str">
-        <v>+94077856852</v>
+        <v>+94774850925</v>
       </c>
       <c r="I53" t="str">
         <v>Main Roster</v>
@@ -3587,16 +3919,16 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>4. D.M.V.I.Dissanayake</v>
+        <v>4. Dinal Akash</v>
       </c>
       <c r="F54" t="str">
-        <v>vortex</v>
+        <v>Dinall</v>
       </c>
       <c r="G54" t="str">
-        <v>vishmi.dissanayake1122@gmail.com</v>
+        <v>randeshdaluwatte@gmail.com</v>
       </c>
       <c r="H54" t="str">
-        <v>+94788943505</v>
+        <v>+94754887389</v>
       </c>
       <c r="I54" t="str">
         <v>Main Roster</v>
@@ -3631,9 +3963,357 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TEAM: PHANTOM SQUAD</v>
+      </c>
+      <c r="B56" t="str">
+        <v>[ APPROVED ]</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Sudhari Rajakaruna (sudharirajakaruna2005@gmail.com)</v>
+      </c>
+      <c r="D56" t="str">
+        <v>+94777531210</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v>1. Rizmiya Rajabdeen</v>
+      </c>
+      <c r="F57" t="str">
+        <v>RushQueen</v>
+      </c>
+      <c r="G57" t="str">
+        <v>rizmiyarajabdeen@gmail.com</v>
+      </c>
+      <c r="H57" t="str">
+        <v>+94768880741</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v>2. Bosadi Kothalawala</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Luna</v>
+      </c>
+      <c r="G58" t="str">
+        <v>bosadithimansha@gmail.com</v>
+      </c>
+      <c r="H58" t="str">
+        <v>+94772564147</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v>3. Navindi Thisarani</v>
+      </c>
+      <c r="F59" t="str">
+        <v>CodCat</v>
+      </c>
+      <c r="G59" t="str">
+        <v>navindithisarani17@gmail.com</v>
+      </c>
+      <c r="H59" t="str">
+        <v>+94771452859</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v/>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v>4. Thisasni Damsiluni</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Twilight</v>
+      </c>
+      <c r="G60" t="str">
+        <v>foreveryoungthisa@gmail.com</v>
+      </c>
+      <c r="H60" t="str">
+        <v>+94712484211</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TEAM: VEX</v>
+      </c>
+      <c r="B62" t="str">
+        <v>[ APPROVED ]</v>
+      </c>
+      <c r="C62" t="str">
+        <v>JEZAN N (jezanjoy@gmail.com)</v>
+      </c>
+      <c r="D62" t="str">
+        <v>+94754860486</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v>1. THUSHANTH</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Thushanth</v>
+      </c>
+      <c r="G63" t="str">
+        <v>chandranthushanth@gmail.com</v>
+      </c>
+      <c r="H63" t="str">
+        <v>+94773328937</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v/>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v>2. RIZNY</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Rizee</v>
+      </c>
+      <c r="G64" t="str">
+        <v>mohamedrizee2005@gmail.com</v>
+      </c>
+      <c r="H64" t="str">
+        <v>+94756166103</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v/>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v>3. Kaveesha Fernando</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Jayden_Roy05</v>
+      </c>
+      <c r="G65" t="str">
+        <v>kaveeshaf12@gmail.com</v>
+      </c>
+      <c r="H65" t="str">
+        <v>+94718685596</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v/>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v>4. Indusara Rathnayake</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Zara_69</v>
+      </c>
+      <c r="G66" t="str">
+        <v>induzara69@gmail.com</v>
+      </c>
+      <c r="H66" t="str">
+        <v>+94719944136</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Main Roster</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I67"/>
   </ignoredErrors>
 </worksheet>
 </file>